--- a/artfynd/A 25270-2022 artfynd.xlsx
+++ b/artfynd/A 25270-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25270-2022 artfynd.xlsx
+++ b/artfynd/A 25270-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17276712</v>
+        <v>17276710</v>
       </c>
       <c r="B2" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579299.9004380065</v>
+        <v>579300</v>
       </c>
       <c r="R2" t="n">
-        <v>6958832.652626404</v>
+        <v>6958833</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -752,19 +747,9 @@
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17276710</v>
+        <v>17277031</v>
       </c>
       <c r="B3" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1588</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579299.9004380065</v>
+        <v>579300</v>
       </c>
       <c r="R3" t="n">
-        <v>6958832.652626404</v>
+        <v>6958833</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -877,19 +857,9 @@
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17276864</v>
+        <v>17276712</v>
       </c>
       <c r="B4" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579299.9004380065</v>
+        <v>579300</v>
       </c>
       <c r="R4" t="n">
-        <v>6958832.652626404</v>
+        <v>6958833</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1002,19 +967,9 @@
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,12 +1008,7 @@
         <v>17276708</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579299.9004380065</v>
+        <v>579300</v>
       </c>
       <c r="R5" t="n">
-        <v>6958832.652626404</v>
+        <v>6958833</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1127,19 +1077,9 @@
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,37 +1115,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17277031</v>
+        <v>17276501</v>
       </c>
       <c r="B6" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2813</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579299.9004380065</v>
+        <v>579300</v>
       </c>
       <c r="R6" t="n">
-        <v>6958832.652626404</v>
+        <v>6958833</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1252,19 +1187,9 @@
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,12 +1228,7 @@
         <v>17276480</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579299.9004380065</v>
+        <v>579300</v>
       </c>
       <c r="R7" t="n">
-        <v>6958832.652626404</v>
+        <v>6958833</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1377,19 +1297,9 @@
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-09-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,15 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17276501</v>
+        <v>17276872</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,21 +1346,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220075</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1469,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579299.9004380065</v>
+        <v>579300</v>
       </c>
       <c r="R8" t="n">
-        <v>6958832.652626404</v>
+        <v>6958833</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1502,19 +1407,9 @@
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-09-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,6 +1438,116 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>17276864</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lövåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579300</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6958833</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövbränna</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mats Dynesius</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 25270-2022 artfynd.xlsx
+++ b/artfynd/A 25270-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276710</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276712</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276708</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276501</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276480</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276872</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,8 +1592,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276864</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>